--- a/datasets/commission_formation/data/output/work_programme_items.xlsx
+++ b/datasets/commission_formation/data/output/work_programme_items.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,18 +483,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Competitiveness Compass</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,18 +521,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Single Market Strategy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Competitiveness</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,18 +559,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>First Omnibus package on sustainability</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -561,18 +597,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Second Omnibus package on investment simplification</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -587,18 +635,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15.</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Third Omnibus package, including on small mid-caps and removal of paper requirements</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -613,18 +673,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Digital package</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -639,18 +711,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>European Business Wallet</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -665,18 +749,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Clean Industrial Deal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Competitiveness and Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -691,18 +787,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Action plan on affordable energy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Competitiveness and Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -717,18 +825,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Industrial Decarbonisation Accelerator Act</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -743,18 +863,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21.</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>EU Start-up and Scale-up Strategy</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Competitiveness and Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,18 +901,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22.</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience</t>
+          <t>Communication on a Savings and Investments Union</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -795,18 +939,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23.</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience</t>
+          <t>Review of the Securitisation Framework</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -821,18 +977,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Digital Networks Act</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,18 +1015,30 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>AI Continent Action Plan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -873,18 +1053,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Quantum Strategy of EU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -899,18 +1091,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>EU Space Act</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -925,18 +1129,30 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28.</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Bioeconomy Strategy</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Competitiveness and Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Non-legislative or legislative</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -951,18 +1167,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>29.</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Social fairness</t>
+          <t>Targeted revision of the REACH Regulation</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -977,18 +1205,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>30.</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Social fairness</t>
+          <t>Roadmap towards ending Russian energy imports</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1003,18 +1243,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Sustainable Transport Investment Plan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Competitiveness and Decarbonisation A new era for European Defence and Security</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1029,18 +1281,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32.</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Social fairness</t>
+          <t>White Paper on the Future of European Defence</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1055,18 +1319,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>33.</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Decarbonisation</t>
+          <t>EU Preparedness Union Strategy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Preparedness and Resilience</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1081,18 +1357,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>34.</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Critical Medicines Act</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Preparedness and Resilience</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1107,18 +1395,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>35.</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Strategy to support medical countermeasures against public health threats</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Preparedness and Resilience</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1133,18 +1433,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>36.</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>EU Stockpiling Strategy</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Preparedness and Resilience</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1159,18 +1471,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>37.</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience</t>
+          <t>New European Internal Security Strategy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1185,18 +1509,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>38.</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>New rules on drug precursors</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1211,18 +1547,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>39.</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Firearms Trafficking Directive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1237,18 +1585,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>40.</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Action plan on the cybersecurity of hospitals and healthcare providers</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1263,18 +1623,30 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>41.</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>New common approach on returns</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1289,18 +1661,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42.</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>European Migration and Asylum Strategy</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1315,18 +1699,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>43.</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>A new action plan to implement the European Pillar of Social Rights</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Social fairness</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1341,18 +1737,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>44.</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Future priority</t>
+          <t>Quality jobs roadmap</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Social fairness</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1367,18 +1775,30 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>45.</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Future priority</t>
+          <t>Union of Skills</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1388,27 +1808,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>2030 Consumer Agenda, including an action plan for consumers in the Single Market</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fitness check on the legislative acquis in the digital policy area</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+          <t>Social fairness Sustaining our quality of life: food security, water and nature</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1418,27 +1846,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>European Climate Law amendment</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fitness check on energy security architecture</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1448,27 +1884,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Q2 / Q3 2025</t>
+          <t>Vision for Agriculture and Food</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fitness check on market access in inland waterway transport</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+          <t>Competitiveness and Decarbonisation</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1478,27 +1922,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Common Agricultural Policy simplification package</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fitness Check of EU airports legislation</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+          <t>Simplification</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1508,27 +1960,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Ocean Pact</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Evaluation of the Public Procurement Directives</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1538,27 +1998,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6.</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>European Water Resilience Strategy</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+          <t>Preparedness and Resilience Protecting our democracy, upholding our values</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1568,27 +2036,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7.</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>European Democracy Shield</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+          <t>Democracy</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1598,27 +2074,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>EU Strategy to support, protect and empower the civil society</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Evaluation of radioactive waste directives</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+          <t>Democracy</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1628,27 +2112,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9.</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Roadmap for Women’s Rights</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1658,27 +2150,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>New equality strategies for LGBTIQ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Evaluation of the EU Lifts Directive</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+          <t>Equality A global Europe: Leveraging our power and partnerships</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1688,27 +2188,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11.</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Pact for the Mediterranean</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1718,27 +2226,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>EU strategic approach to the Black Sea/ Black Sea Strategy</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1748,27 +2264,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Q1/Q2 2025</t>
+          <t>Joint Communication on a new Strategic EU-India Agenda</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Evaluation of the Fishing Vessel Safety Directive</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+          <t>Geopolitics Delivering together and preparing our Union for the future</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1778,27 +2302,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Post-2027 Multiannual Financial Framework proposals</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+          <t>Future priority</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1813,7 +2345,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>15.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1824,7 +2356,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Evaluation of State aid rules for banks in difficulties</t>
+          <t>Fitness check on the legislative acquis in the digital policy area</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -1843,18 +2375,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>16.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Evaluation of the Guarantee Notice</t>
+          <t>Fitness check on energy security architecture</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -1873,18 +2405,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>17.</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 / Q3 2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
+          <t>Fitness check on market access in inland waterway transport</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -1903,7 +2435,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>18.</t>
+          <t>4.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1914,7 +2446,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Evaluation of EU Rules of Origin</t>
+          <t>Fitness Check of EU airports legislation</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -1933,18 +2465,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>19.</t>
+          <t>5.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Evaluation of the Defence Transfers Directive</t>
+          <t>Evaluation of the Public Procurement Directives</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -1963,7 +2495,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20.</t>
+          <t>6.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1974,7 +2506,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Evaluation of the Firearms Directive</t>
+          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -1993,7 +2525,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>21.</t>
+          <t>7.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2004,7 +2536,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Evaluation on the Innovation Fund</t>
+          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2023,7 +2555,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>22.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2034,7 +2566,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Evaluation on the Modernisation Fund</t>
+          <t>Evaluation of radioactive waste directives</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2053,18 +2585,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>23.</t>
+          <t>9.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2083,18 +2615,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>10.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Q3/Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+          <t>Evaluation of the EU Lifts Directive</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2113,18 +2645,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>25.</t>
+          <t>11.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2143,18 +2675,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>26.</t>
+          <t>12.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2173,18 +2705,18 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>27.</t>
+          <t>13.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1/Q2 2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+          <t>Evaluation of the Fishing Vessel Safety Directive</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2203,18 +2735,18 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>28.</t>
+          <t>14.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2233,18 +2765,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>29.</t>
+          <t>15.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+          <t>Evaluation of State aid rules for banks in difficulties</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2263,7 +2795,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>30.</t>
+          <t>16.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2274,7 +2806,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+          <t>Evaluation of the Guarantee Notice</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2293,18 +2825,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>17.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Q1-Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the European Defence Fund</t>
+          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2323,18 +2855,18 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>32.</t>
+          <t>18.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+          <t>Evaluation of EU Rules of Origin</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2353,18 +2885,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>33.</t>
+          <t>19.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+          <t>Evaluation of the Defence Transfers Directive</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2383,7 +2915,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>34.</t>
+          <t>20.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2394,7 +2926,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+          <t>Evaluation of the Firearms Directive</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2408,26 +2940,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>35.</t>
+          <t>21.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Evaluation on the Innovation Fund</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2438,26 +2970,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>36.</t>
+          <t>22.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Evaluation on the Modernisation Fund</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2468,26 +3000,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>37.</t>
+          <t>23.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -2498,35 +3030,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>COM(2011)714 final Proposal for a COUNCIL DIRECTIVE on a common system of taxation Obsolete – the scope of the proposal has been partly</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2011/0314 (CNS) applicable to interest and royalty payments made between associated companies taken over by the Directive implementing the OECD of different Member States Pillar 2 on minimum corporate taxation. The remaining issues the proposal intended to tackle will be addressed via an upcoming Omnibus act as a part of the simplification process.</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+          <t>Q3/Q4 2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2536,35 +3060,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>COM(2011)827 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the proposal is by now obsolete. The</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2011/0391 (COD) THE COUNCIL on common rules for the allocation of slots at European Union Commission has launched a fitness-check and will airports decide on the basis of its findings on the way forward.</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2574,35 +3090,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>COM(2012)336 final Proposal for a COUNCIL REGULATION establishing a facility for providing Obsolete – the proposal needs to be updated as regards</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2012/0164 (APP) financial assistance for Member States whose currency is not the euro i.a. the funding modalities of the Balance of Payments Facility and to integrate the lessons to be drawn from the recent crises, as well as the institutional, economic and financial sector developments since 2009, and their possible implication for the design and implementation of the facility, in line with the Council Conclusions of 27 March 2024.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2612,35 +3120,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>COM(2015)603 final Proposal for a COUNCIL DECISION laying down measures in view of No foreseeable agreement – in the context of the</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2015/0250 (NLE) progressively establishing unified representation of the euro area in the discussions on Europe’s economic and financial International Monetary Fund sovereignty, the Commission will assess whether another proposal should be tabled or another type of approach should be chosen. 2 This list includes pending legislative proposals, which the Commission intends to withdraw within six months 22 No. References Title Reasons for withdrawal</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2650,35 +3150,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>COM(2017)276 final Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the No foreseeable agreement – the proposal is blocked with</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2017/0115 (CNS) charging of heavy goods vehicles for the use of certain infrastructures, as regards no perspective of agreement. certain provisions on vehicle taxation</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2688,35 +3180,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>COM(2017)647 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal has not been</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2017/0288 (COD) THE COUNCIL amending Regulation (EC) No 1073/2009 on common rules for taken up for discussion in the Council and is by now access to the international market for coach and bus services outdated.</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2726,35 +3210,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>COM(2017)827 final Proposal for a COUNCIL REGULATION on the establishment of the European No foreseeable agreement - many of the changes</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2017/0333 (APP) Monetary Fund proposed under this initiative have been incorporated into a separate revision of the European Stability Mechanism Treaty.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2764,35 +3240,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>COM(2018)135 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2018/0063B (COD) THE COUNCIL on credit servicers, credit purchasers and the recovery of further progress is unlikely. collateral</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>Q1-Q2 2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Interim Evaluation of the European Defence Fund</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2802,35 +3270,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>COM(2018)329 final Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as No foreseeable agreement – discussions are suspended</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2018/0164(CNS) regards the introduction of the detailed technical measures for the operation of since 2019 and further progress is unlikely. the definitive VAT system for the taxation of trade between Member States</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2840,35 +3300,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>COM(2018)339 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2018/0171 (COD) THE COUNCIL on sovereign bond-backed securities further progress is unlikely.</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2878,35 +3330,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>34.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>COM(2018)387 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - The proposal is outdated</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2018/0212 (COD) THE COUNCIL on the establishment of a European Investment Stabilisation with the entry into force of NGEU and the Recovery and Function Resilience Facility (RRF) and the withdrawal of the so- called Budgetary Instrument for Convergence and Competitiveness (BICC) in February 2021.</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,33 +3360,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>COM(2019)38 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2019/0017 (COD) THE COUNCIL amending Regulation (EU) 2015/757 in order to take incorporated into the most recent EU ETS revision, appropriate account of the global data collection system for ship fuel oil adopted in 2023. consumption data</t>
-        </is>
-      </c>
+          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2954,33 +3390,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>COM(2020)49 final Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field Obsolete - since the adoption of this proposal in 2020, a</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2020/0022 (CNS) of taxation (codification) number of significant amendments have been adopted, making this codification proposal obsolete. The Commission will propose a new codified proposal. 23 No. References Title Reasons for withdrawal</t>
-        </is>
-      </c>
+          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2992,33 +3420,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>37.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>COM(2020)577 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2020/0264 (COD) THE COUNCIL amending Regulation (EU) 2018/1139 as regards the capacity incorporated into the Single European Sky ("SES II +") of the European Union Aviation Safety Agency to act as Performance Review Regulation. Body of the Single European Sky</t>
-        </is>
-      </c>
+          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3035,17 +3455,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>COM(2021)769 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - since the adoption of this proposal in 2021, a</t>
+          <t>COM(2011)714 final Proposal for a COUNCIL DIRECTIVE on a common system of taxation Obsolete – the scope of the proposal has been partly</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2021/0400 (COD) THE COUNCIL laying down for certain road vehicles circulating within the recent amendment has been proposed by the Union the maximum authorised dimensions in national and international traffic Commission, that will make this codification proposal and the maximum authorised weights in international traffic (codification) obsolete. The Commission will propose a new codified proposal as soon as the new amendment will have been adopted.</t>
+          <t>2011/0314 (CNS) applicable to interest and royalty payments made between associated companies taken over by the Directive implementing the OECD of different Member States Pillar 2 on minimum corporate taxation. The remaining issues the proposal intended to tackle will be addressed via an upcoming Omnibus act as a part of the simplification process.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -3056,7 +3476,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -3073,28 +3493,28 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>COM(2022)222 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the changes suggested by this proposal were</t>
+          <t>COM(2011)827 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the proposal is by now obsolete. The</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2022/0160 (COD) THE COUNCIL amending Directive (EU) 2018/2001 on the promotion of the incorporated during the discussions on the revision of use of energy from renewable sources, Directive 2010/31/EU on the energy the Energy Performance of Buildings Directive, the performance of buildings and Directive 2012/27/EU on energy efficiency Energy Efficiency Directive and the Renewable Energy Directive.</t>
+          <t>2011/0391 (COD) THE COUNCIL on common rules for the allocation of slots at European Union Commission has launched a fitness-check and will airports decide on the basis of its findings on the way forward.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2011</t>
         </is>
       </c>
     </row>
@@ -3111,17 +3531,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>COM(2023)232 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>COM(2012)336 final Proposal for a COUNCIL REGULATION establishing a facility for providing Obsolete – the proposal needs to be updated as regards</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2023/0133(COD) THE COUNCIL on standard essential patents and amending Regulation whether another proposal should be tabled or another (EU)2017/1001 type of approach should be chosen. A new era for European Defence and Security</t>
+          <t>2012/0164 (APP) financial assistance for Member States whose currency is not the euro i.a. the funding modalities of the Balance of Payments Facility and to integrate the lessons to be drawn from the recent crises, as well as the institutional, economic and financial sector developments since 2009, and their possible implication for the design and implementation of the facility, in line with the Council Conclusions of 27 March 2024.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3132,7 +3552,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
     </row>
@@ -3149,28 +3569,28 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>COM(2018)634 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the Commission intends to present a new</t>
+          <t>COM(2015)603 final Proposal for a COUNCIL DECISION laying down measures in view of No foreseeable agreement – in the context of the</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2018/0329 (COD) THE COUNCIL on common standards and procedures in Member States for proposal in 2025 (referred to in annex 1 of this returning illegally staying third-country nationals (recast) A contribution from Commission Work Programme) in the context of which the European Commission to the Leaders’ meeting in Salzburg on 19-20 the current pending proposal will be effectively September 2018 withdrawn.</t>
+          <t>2015/0250 (NLE) progressively establishing unified representation of the euro area in the discussions on Europe’s economic and financial International Monetary Fund sovereignty, the Commission will assess whether another proposal should be tabled or another type of approach should be chosen. 2 This list includes pending legislative proposals, which the Commission intends to withdraw within six months 22 No. References Title Reasons for withdrawal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>DECISION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -3187,28 +3607,28 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>COM(2021)890 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the content of this proposal was merged into</t>
+          <t>COM(2017)276 final Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the No foreseeable agreement – the proposal is blocked with</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2021/0427 (COD) THE COUNCIL addressing situations of instrumentalisation in the field of Regulation (EU) 2024/1359 addressing situations of migration and asylum crisis and force majeure in the field of migration and asylum and amending Regulation (EU) 2021/1147.</t>
+          <t>2017/0115 (CNS) charging of heavy goods vehicles for the use of certain infrastructures, as regards no perspective of agreement. certain provisions on vehicle taxation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -3225,28 +3645,28 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>COM(2021)752 final Proposal for a COUNCIL DECISION on provisional emergency measures for Obsolete – the proposal was blocked during the inter-</t>
+          <t>COM(2017)647 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal has not been</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2021/0401 (CNS) the benefit of Latvia, Lithuania and Poland institutional discussions and is now obsolete. 24 No. References Title Reasons for withdrawal</t>
+          <t>2017/0288 (COD) THE COUNCIL amending Regulation (EC) No 1073/2009 on common rules for taken up for discussion in the Council and is by now access to the international market for coach and bus services outdated.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -3263,28 +3683,28 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>COM(2024)174 final Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Obsolete – no agreement was foreseeable. The Schengen</t>
+          <t>COM(2017)827 final Proposal for a COUNCIL REGULATION on the establishment of the European No foreseeable agreement - many of the changes</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2024/0094 (NLE) Cycle Council agreed on a number of priority areas for action that are dealt with via other means than this proposal. Sustaining our quality of life: food security, water and nature</t>
+          <t>2017/0333 (APP) Monetary Fund proposed under this initiative have been incorporated into a separate revision of the European Stability Mechanism Treaty.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>RECOMMENDATION</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
@@ -3301,28 +3721,28 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>COM(2012)403 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>COM(2018)135 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2012/0196 (COD) THE COUNCIL on the protection of species of wild fauna and flora by regulating Furthermore, since 2012, developments took place that trade therein (Recast) make this proposal obsolete. The Commission will assess whether another proposal should be tabled or another type of approach should be chosen to allow for a new start.</t>
+          <t>2018/0063B (COD) THE COUNCIL on credit servicers, credit purchasers and the recovery of further progress is unlikely. collateral</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -3339,28 +3759,28 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>COM(2015)177 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - any potential further</t>
+          <t>COM(2018)329 final Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as No foreseeable agreement – discussions are suspended</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2015/0093 (COD) THE COUNCIL amending Regulation (EC) No 1829/2003 as regards the amendment of the GMO legislation will depend on the possibility for the Member States to restrict or prohibit the use of genetically outcome of the negotiations on the proposal for new modified food and feed on their territory genomic techniques, or the identification of issues to be addressed in the context of the biotechnology and biomanufacturing initiative.</t>
+          <t>2018/0164(CNS) regards the introduction of the detailed technical measures for the operation of since 2019 and further progress is unlikely. the definitive VAT system for the taxation of trade between Member States</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -3377,17 +3797,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>COM(2022)563 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>COM(2018)339 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2022/0348 (COD) THE COUNCIL laying down management, conservation and control measures between the European Parliament and the Council at applicable in the Area of the Southern Indian Ocean Fisheries Agreement first reading. The Commission intends to present a new (SIOFA) proposal in 2025 in the context of which the current pending proposal will be effectively withdrawn.</t>
+          <t>2018/0171 (COD) THE COUNCIL on sovereign bond-backed securities further progress is unlikely.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3398,7 +3818,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3835,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>COM(2023)771 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>COM(2018)387 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - The proposal is outdated</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2023/0449 (COD) THE COUNCIL amending Regulations (EU) 2016/1139, (EU) 2018/973 and from the colegislators. (EU) 2019/472 as regards the targets for fixing fishing opportunities Protecting our democracy, upholding our values</t>
+          <t>2018/0212 (COD) THE COUNCIL on the establishment of a European Investment Stabilisation with the entry into force of NGEU and the Recovery and Function Resilience Facility (RRF) and the withdrawal of the so- called Budgetary Instrument for Convergence and Competitiveness (BICC) in February 2021.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -3436,7 +3856,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -3453,28 +3873,28 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>COM(2008)426 final Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal No foreseeable agreement – the proposal is blocked and</t>
+          <t>COM(2019)38 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2008/0140 (CNS) treatment between persons irrespective of religion or belief, disability, age or further progress is unlikely. sexual orientation 25 No. References Title Reasons for withdrawal</t>
+          <t>2019/0017 (COD) THE COUNCIL amending Regulation (EU) 2015/757 in order to take incorporated into the most recent EU ETS revision, appropriate account of the global data collection system for ship fuel oil adopted in 2023. consumption data</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
@@ -3491,28 +3911,28 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>COM(2011)137 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement - no progress has been made</t>
+          <t>COM(2020)49 final Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field Obsolete - since the adoption of this proposal in 2020, a</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2011/0073 (COD) OF THE COUNCIL amending Regulation (EC) No 1049/2001 regarding public since 2011. access to European Parliament, Council and Commission documents COM(2008)229 final 2008/0090 (COD)</t>
+          <t>2020/0022 (CNS) of taxation (codification) number of significant amendments have been adopted, making this codification proposal obsolete. The Commission will propose a new codified proposal. 23 No. References Title Reasons for withdrawal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -3529,17 +3949,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>COM(2016)799 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement – the proposal is blocked and</t>
+          <t>COM(2020)577 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2016/0400B (COD) OF THE COUNCIL adapting a number of legal acts providing for the use of the further progress is unlikely. There is a legal obligation regulatory procedure with scrutiny to Articles 290 and 291 of the Treaty on the to put legal acts adopted prior to the entry into force of Functioning of the European Union the Treaty of Lisbon in conformity with Articles 290 and 291 TFEU. The Commission will therefore present to the colegislators a new proposal to that effect.</t>
+          <t>2020/0264 (COD) THE COUNCIL amending Regulation (EU) 2018/1139 as regards the capacity incorporated into the Single European Sky ("SES II +") of the European Union Aviation Safety Agency to act as Performance Review Regulation. Body of the Single European Sky</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -3550,7 +3970,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -3567,28 +3987,28 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>COM(2017)10 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>COM(2021)769 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - since the adoption of this proposal in 2021, a</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2017/0003 (COD) THE COUNCIL concerning the respect for private life and the protection of from the colegislators. Furthermore, the proposal is personal data in electronic communications and repealing Directive 2002/58/EC outdated in view of some recent legislation in both the (Regulation on Privacy and Electronic Communications technological and the legislative landscape.</t>
+          <t>2021/0400 (COD) THE COUNCIL laying down for certain road vehicles circulating within the recent amendment has been proposed by the Union the maximum authorised dimensions in national and international traffic Commission, that will make this codification proposal and the maximum authorised weights in international traffic (codification) obsolete. The Commission will propose a new codified proposal as soon as the new amendment will have been adopted.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -3605,28 +4025,28 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>COM(2017)85 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>COM(2022)222 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the changes suggested by this proposal were</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2017/0035 (COD) THE COUNCIL amending Regulation (EU) No 182/2011 laying down the rules further progress is unlikely. and general principles concerning mechanisms for control by Member States of the Commission’s exercise of implementing powers</t>
+          <t>2022/0160 (COD) THE COUNCIL amending Directive (EU) 2018/2001 on the promotion of the incorporated during the discussions on the revision of use of energy from renewable sources, Directive 2010/31/EU on the energy the Energy Performance of Buildings Directive, the performance of buildings and Directive 2012/27/EU on energy efficiency Energy Efficiency Directive and the Renewable Energy Directive.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>DIRECTIVE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3643,17 +4063,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>COM(2018)96 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>COM(2023)232 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2018/0044 (COD) THE COUNCIL on the law applicable to the third-party effects of assignments further progress is unlikely. of claims</t>
+          <t>2023/0133(COD) THE COUNCIL on standard essential patents and amending Regulation whether another proposal should be tabled or another (EU)2017/1001 type of approach should be chosen. A new era for European Defence and Security</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -3664,7 +4084,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3681,17 +4101,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>COM(2022)496 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>COM(2018)634 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the Commission intends to present a new</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2022/0303 (COD) THE COUNCIL on adapting non-contractual civil liability rules to artificial whether another proposal should be tabled or another intelligence (AI Liability) type of approach should be chosen. A global Europe: Leveraging our power and partnerships</t>
+          <t>2018/0329 (COD) THE COUNCIL on common standards and procedures in Member States for proposal in 2025 (referred to in annex 1 of this returning illegally staying third-country nationals (recast) A contribution from Commission Work Programme) in the context of which the European Commission to the Leaders’ meeting in Salzburg on 19-20 the current pending proposal will be effectively September 2018 withdrawn.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -3702,7 +4122,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
@@ -3719,28 +4139,28 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>JOIN(2015)36 final Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the Obsolete – the ratification process of this agreement has</t>
+          <t>COM(2021)890 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the content of this proposal was merged into</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2015/0302 (NLE) European Union, of the Cooperation Agreement on Partnership and Development been interrupted with the establishment of a Taliban between the European Union and the Islamic Republic of Afghanistan appointed caretaker government that, to date, remains unrecognized by the international community, making the original agreement obsolete. 26 No. References Title Reasons for withdrawal</t>
+          <t>2021/0427 (COD) THE COUNCIL addressing situations of instrumentalisation in the field of Regulation (EU) 2024/1359 addressing situations of migration and asylum crisis and force majeure in the field of migration and asylum and amending Regulation (EU) 2021/1147.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -3757,17 +4177,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>COM(2022)63 final Proposal for a COUNCIL DECISION on the position to be taken on behalf of the Obsolete - the proposal was made in the negotiations on</t>
+          <t>COM(2021)752 final Proposal for a COUNCIL DECISION on provisional emergency measures for Obsolete – the proposal was blocked during the inter-</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2022/0043 (NLE) European Union in the written procedure by the Participants to the Arrangement the modernisation of the Arrangement on Officially on Officially Supported Export Credits amending Annex IV Supported Export Credits, which were finalised in 2023. The content of this proposal was included in another Council decision making this one redundant. Delivering together and preparing our Union for the future</t>
+          <t>2021/0401 (CNS) the benefit of Latvia, Lithuania and Poland institutional discussions and is now obsolete. 24 No. References Title Reasons for withdrawal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -3778,7 +4198,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -3795,28 +4215,28 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>COM(2022)184 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the content of the proposal has been adopted</t>
+          <t>COM(2024)174 final Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Obsolete – no agreement was foreseeable. The Schengen</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2022/0125 (COD) THE COUNCIL amending Regulation (EU, Euratom) 2018/1046 on the financial end of September 2024 as part of the revision of the rules applicable to the general budget of the Union Financial Regulation (Recast).</t>
+          <t>2024/0094 (NLE) Cycle Council agreed on a number of priority areas for action that are dealt with via other means than this proposal. Sustaining our quality of life: food security, water and nature</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>REGULATION</t>
+          <t>RECOMMENDATION</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -3833,17 +4253,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>COM(2024)301 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>COM(2012)403 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024/0059 (COD) THE COUNCIL amending Regulation (EU) 2021/1148 as regards the financial Furthermore, the MFF mid-term revision can be envelope and the allocation for the thematic facility implemented without this legal proposal.</t>
+          <t>2012/0196 (COD) THE COUNCIL on the protection of species of wild fauna and flora by regulating Furthermore, since 2012, developments took place that trade therein (Recast) make this proposal obsolete. The Commission will assess whether another proposal should be tabled or another type of approach should be chosen to allow for a new start.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -3854,7 +4274,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
     </row>
@@ -3871,17 +4291,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>COM(2024)100 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>COM(2015)177 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - any potential further</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024/0060 (COD) THE COUNCIL amending Regulation (EU) No 2021/522, Regulation (EU) No The MFF mid-term revision can be implemented 2021/1057, Regulation (EU) No 2021/1060, Regulation (EU) No 2021/1139, without this legal proposal. An amendment to the Regulation (EU) No 2021/1229 and Regulation (EU) No 2021/1775 as regards Regulation 2021/1755 establishing the Brexit the changes to the amounts of funds for certain programmes and funds Adjustment Reserve (BAR) to establish the legal basis for redistribution of the outstanding amounts between the Member States will be proposed by the Commission in 2025. 27 Annex V: Envisaged repeals No. Policy area Title Reasons for repeal</t>
+          <t>2015/0093 (COD) THE COUNCIL amending Regulation (EC) No 1829/2003 as regards the amendment of the GMO legislation will depend on the possibility for the Member States to restrict or prohibit the use of genetically outcome of the negotiations on the proposal for new modified food and feed on their territory genomic techniques, or the identification of issues to be addressed in the context of the biotechnology and biomanufacturing initiative.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -3892,7 +4312,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
@@ -3909,28 +4329,28 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Agriculture Council Regulation (EC)No 870/2004 of 26 This Community programme was established for the period 2004 to 2006 to complement and</t>
+          <t>COM(2022)563 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>April 2004 establishing a Community promote, at Community level, the work undertaken in the Member States for the conservation, programme on the conservation, characterisation, collection and utilisation of genetic resources in agriculture. Support under this characterisation, collection and utilisation of programme is no longer available, since all Common Agricultural Policy (CAP) support is currently genetic resources in agriculture and repealing granted under the ongoing rural development programmes (until 2025) and national CAP Strategic Regulation (EC) No 1467/94 Plans (until 2027), following Regulation (EU) 1305/2013 and Regulation (EU) 2021/2115 respectively, making this regulation obsolete.</t>
+          <t>2022/0348 (COD) THE COUNCIL laying down management, conservation and control measures between the European Parliament and the Council at applicable in the Area of the Southern Indian Ocean Fisheries Agreement first reading. The Commission intends to present a new (SIOFA) proposal in 2025 in the context of which the current pending proposal will be effectively withdrawn.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3947,28 +4367,28 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>European statistics Council Regulation (EEC) No 3037/90 of 9 The classification from 1990 is obsolete. The current statistical classification of economic</t>
+          <t>COM(2023)771 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>October 1990 on the statistical classification of activities’ in the European Community (NACE) is established in Regulation (EC) No 1893/2006 economic activities in the European of the European Parliament and of the Council of 20 December 2006, as last amended by Community Commission Delegated Regulation (EU) 2023/137 of 10 October 2022.</t>
+          <t>2023/0449 (COD) THE COUNCIL amending Regulations (EU) 2016/1139, (EU) 2018/973 and from the colegislators. (EU) 2019/472 as regards the targets for fixing fishing opportunities Protecting our democracy, upholding our values</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -3985,26 +4405,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>European statistics Council Decision of 25 June 1996 on improving The Decision is obsolete. It has been superseded by new regulations on agricultural statistics</t>
+          <t>COM(2008)426 final Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal No foreseeable agreement – the proposal is blocked and</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Community agricultural statistics (96/411/EC) (integrated farm statistics, agricultural input and output, economic accounts for agriculture).</t>
+          <t>2008/0140 (CNS) treatment between persons irrespective of religion or belief, disability, age or further progress is unlikely. sexual orientation 25 No. References Title Reasons for withdrawal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4019,26 +4443,554 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Road freight Council Regulation (EEC) No 4058/89 of 21 Modern EU legislation has introduced a comprehensive framework that regulates road transport,</t>
+          <t>COM(2011)137 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement - no progress has been made</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>transport December 1989 on the fixing of rates for the focusing on safety, environmental standards, and fair competition without the need for rate-fixing. carriage of goods by road between Member Regulations such as Regulation (EC) No 1071/2009, Regulation (EC) No 1072/2009, and States Regulation (EC) No 1073/2009 have effectively superseded the need for the provisions outlined in Council Regulation (EEC) No 4058/89, rendering it redundant. 28</t>
+          <t>2011/0073 (COD) OF THE COUNCIL amending Regulation (EC) No 1049/2001 regarding public since 2011. access to European Parliament, Council and Commission documents COM(2008)229 final 2008/0090 (COD)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulation</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WP114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>COM(2016)799 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement – the proposal is blocked and</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2016/0400B (COD) OF THE COUNCIL adapting a number of legal acts providing for the use of the further progress is unlikely. There is a legal obligation regulatory procedure with scrutiny to Articles 290 and 291 of the Treaty on the to put legal acts adopted prior to the entry into force of Functioning of the European Union the Treaty of Lisbon in conformity with Articles 290 and 291 TFEU. The Commission will therefore present to the colegislators a new proposal to that effect.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>WP115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>COM(2017)10 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2017/0003 (COD) THE COUNCIL concerning the respect for private life and the protection of from the colegislators. Furthermore, the proposal is personal data in electronic communications and repealing Directive 2002/58/EC outdated in view of some recent legislation in both the (Regulation on Privacy and Electronic Communications technological and the legislative landscape.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WP116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>COM(2017)85 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2017/0035 (COD) THE COUNCIL amending Regulation (EU) No 182/2011 laying down the rules further progress is unlikely. and general principles concerning mechanisms for control by Member States of the Commission’s exercise of implementing powers</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WP117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>COM(2018)96 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2018/0044 (COD) THE COUNCIL on the law applicable to the third-party effects of assignments further progress is unlikely. of claims</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>WP118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>COM(2022)496 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2022/0303 (COD) THE COUNCIL on adapting non-contractual civil liability rules to artificial whether another proposal should be tabled or another intelligence (AI Liability) type of approach should be chosen. A global Europe: Leveraging our power and partnerships</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WP119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>JOIN(2015)36 final Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the Obsolete – the ratification process of this agreement has</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2015/0302 (NLE) European Union, of the Cooperation Agreement on Partnership and Development been interrupted with the establishment of a Taliban between the European Union and the Islamic Republic of Afghanistan appointed caretaker government that, to date, remains unrecognized by the international community, making the original agreement obsolete. 26 No. References Title Reasons for withdrawal</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WP120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>COM(2022)63 final Proposal for a COUNCIL DECISION on the position to be taken on behalf of the Obsolete - the proposal was made in the negotiations on</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2022/0043 (NLE) European Union in the written procedure by the Participants to the Arrangement the modernisation of the Arrangement on Officially on Officially Supported Export Credits amending Annex IV Supported Export Credits, which were finalised in 2023. The content of this proposal was included in another Council decision making this one redundant. Delivering together and preparing our Union for the future</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WP121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>COM(2022)184 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the content of the proposal has been adopted</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2022/0125 (COD) THE COUNCIL amending Regulation (EU, Euratom) 2018/1046 on the financial end of September 2024 as part of the revision of the rules applicable to the general budget of the Union Financial Regulation (Recast).</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>WP122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>COM(2024)301 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2024/0059 (COD) THE COUNCIL amending Regulation (EU) 2021/1148 as regards the financial Furthermore, the MFF mid-term revision can be envelope and the allocation for the thematic facility implemented without this legal proposal.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>WP123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>COM(2024)100 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2024/0060 (COD) THE COUNCIL amending Regulation (EU) No 2021/522, Regulation (EU) No The MFF mid-term revision can be implemented 2021/1057, Regulation (EU) No 2021/1060, Regulation (EU) No 2021/1139, without this legal proposal. An amendment to the Regulation (EU) No 2021/1229 and Regulation (EU) No 2021/1775 as regards Regulation 2021/1755 establishing the Brexit the changes to the amounts of funds for certain programmes and funds Adjustment Reserve (BAR) to establish the legal basis for redistribution of the outstanding amounts between the Member States will be proposed by the Commission in 2025. 27 Annex V: Envisaged repeals No. Policy area Title Reasons for repeal</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WP124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Agriculture Council Regulation (EC)No 870/2004 of 26 This Community programme was established for the period 2004 to 2006 to complement and</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>April 2004 establishing a Community promote, at Community level, the work undertaken in the Member States for the conservation, programme on the conservation, characterisation, collection and utilisation of genetic resources in agriculture. Support under this characterisation, collection and utilisation of programme is no longer available, since all Common Agricultural Policy (CAP) support is currently genetic resources in agriculture and repealing granted under the ongoing rural development programmes (until 2025) and national CAP Strategic Regulation (EC) No 1467/94 Plans (until 2027), following Regulation (EU) 1305/2013 and Regulation (EU) 2021/2115 respectively, making this regulation obsolete.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WP125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>European statistics Council Regulation (EEC) No 3037/90 of 9 The classification from 1990 is obsolete. The current statistical classification of economic</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>October 1990 on the statistical classification of activities’ in the European Community (NACE) is established in Regulation (EC) No 1893/2006 economic activities in the European of the European Parliament and of the Council of 20 December 2006, as last amended by Community Commission Delegated Regulation (EU) 2023/137 of 10 October 2022.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WP126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>European statistics Council Decision of 25 June 1996 on improving The Decision is obsolete. It has been superseded by new regulations on agricultural statistics</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Community agricultural statistics (96/411/EC) (integrated farm statistics, agricultural input and output, economic accounts for agriculture).</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WP127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Road freight Council Regulation (EEC) No 4058/89 of 21 Modern EU legislation has introduced a comprehensive framework that regulates road transport,</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>transport December 1989 on the fixing of rates for the focusing on safety, environmental standards, and fair competition without the need for rate-fixing. carriage of goods by road between Member Regulations such as Regulation (EC) No 1071/2009, Regulation (EC) No 1072/2009, and States Regulation (EC) No 1073/2009 have effectively superseded the need for the provisions outlined in Council Regulation (EEC) No 4058/89, rendering it redundant. 28</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>2009</t>
         </is>

--- a/datasets/commission_formation/data/output/work_programme_items.xlsx
+++ b/datasets/commission_formation/data/output/work_programme_items.xlsx
@@ -2350,17 +2350,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Fitness check on the legislative acquis in the digital policy area</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Fitness check on the legislative acquis in the digital policy area</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Fitness check on energy security architecture</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Fitness check on energy security architecture</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Fitness check on market access in inland waterway transport</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>Q2 / Q3 2025</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Fitness check on market access in inland waterway transport</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Fitness Check of EU airports legislation</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Fitness Check of EU airports legislation</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>Evaluation of the Public Procurement Directives</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Evaluation of the Public Procurement Directives</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>Evaluation of radioactive waste directives</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Evaluation of radioactive waste directives</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2620,17 +2620,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>Evaluation of the EU Lifts Directive</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Evaluation of the EU Lifts Directive</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2680,17 +2680,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>Evaluation of the Fishing Vessel Safety Directive</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>Q1/Q2 2025</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Evaluation of the Fishing Vessel Safety Directive</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2770,17 +2770,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>Evaluation of State aid rules for banks in difficulties</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Evaluation of State aid rules for banks in difficulties</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2800,17 +2800,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>Evaluation of the Guarantee Notice</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Evaluation of the Guarantee Notice</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2860,17 +2860,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Evaluation of EU Rules of Origin</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Evaluation of EU Rules of Origin</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2890,17 +2890,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Evaluation of the Defence Transfers Directive</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Evaluation of the Defence Transfers Directive</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Evaluation of the Firearms Directive</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Evaluation of the Firearms Directive</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>Evaluation on the Innovation Fund</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Evaluation on the Innovation Fund</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Evaluation on the Modernisation Fund</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Evaluation on the Modernisation Fund</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3040,17 +3040,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>Q3/Q4 2025</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3070,17 +3070,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3160,17 +3160,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3250,17 +3250,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Interim Evaluation of the European Defence Fund</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>Q1-Q2 2025</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Interim Evaluation of the European Defence Fund</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Interim evaluation of the Customs 2021-2027 programme</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">

--- a/datasets/commission_formation/data/output/work_programme_items.xlsx
+++ b/datasets/commission_formation/data/output/work_programme_items.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,12 +673,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Digital package</t>
+          <t>Revision of the Sustainable Finance Disclosure Regulation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -711,12 +711,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>European Business Wallet</t>
+          <t>Digital package</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -749,28 +749,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Clean Industrial Deal</t>
+          <t>European Business Wallet</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Action plan on affordable energy</t>
+          <t>Clean Industrial Deal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -825,12 +825,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Industrial Decarbonisation Accelerator Act</t>
+          <t>Action plan on affordable energy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -841,12 +841,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EU Start-up and Scale-up Strategy</t>
+          <t>Industrial Decarbonisation Accelerator Act</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -879,12 +879,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -901,18 +901,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Communication on a Savings and Investments Union</t>
+          <t>EU Start-up and Scale-up Strategy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Review of the Securitisation Framework</t>
+          <t>Communication on a Savings and Investments Union</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -955,12 +955,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -977,18 +977,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Digital Networks Act</t>
+          <t>Review of the Securitisation Framework</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Continent Action Plan</t>
+          <t>Digital Networks Act</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Quantum Strategy of EU</t>
+          <t>AI Continent Action Plan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1091,23 +1091,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EU Space Act</t>
+          <t>Quantum Strategy of EU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1129,28 +1129,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bioeconomy Strategy</t>
+          <t>EU Space Act</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Non-legislative or legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -1167,23 +1167,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Targeted revision of the REACH Regulation</t>
+          <t>Bioeconomy Strategy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative or legislative</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1205,28 +1205,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Roadmap towards ending Russian energy imports</t>
+          <t>Targeted revision of the REACH Regulation</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -1243,18 +1243,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sustainable Transport Investment Plan</t>
+          <t>Roadmap towards ending Russian energy imports</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation A new era for European Defence and Security</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1281,18 +1281,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>White Paper on the Future of European Defence</t>
+          <t>Sustainable Transport Investment Plan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -1319,18 +1319,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EU Preparedness Union Strategy</t>
+          <t>White Paper on the Future of European Defence</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Critical Medicines Act</t>
+          <t>EU Preparedness Union Strategy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Strategy to support medical countermeasures against public health threats</t>
+          <t>Critical Medicines Act</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EU Stockpiling Strategy</t>
+          <t>Strategy to support medical countermeasures against public health threats</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1471,18 +1471,18 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>New European Internal Security Strategy</t>
+          <t>EU Stockpiling Strategy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Preparedness and Resilience</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>New rules on drug precursors</t>
+          <t>New European Internal Security Strategy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Firearms Trafficking Directive</t>
+          <t>New rules on drug precursors</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Action plan on the cybersecurity of hospitals and healthcare providers</t>
+          <t>Firearms Trafficking Directive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -1623,23 +1623,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>New common approach on returns</t>
+          <t>Action plan on the cybersecurity of hospitals and healthcare providers</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>European Migration and Asylum Strategy</t>
+          <t>New common approach on returns</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1699,18 +1699,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A new action plan to implement the European Pillar of Social Rights</t>
+          <t>European Migration and Asylum Strategy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Social fairness</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Quality jobs roadmap</t>
+          <t>A new action plan to implement the European Pillar of Social Rights</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1775,18 +1775,18 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Union of Skills</t>
+          <t>Quality jobs roadmap</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Social fairness</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -1813,18 +1813,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2030 Consumer Agenda, including an action plan for consumers in the Single Market</t>
+          <t>Union of Skills</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Social fairness Sustaining our quality of life: food security, water and nature</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1851,28 +1851,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>European Climate Law amendment</t>
+          <t>2030 Consumer Agenda, including an action plan for consumers in the Single Market</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Decarbonisation</t>
+          <t>Social fairness</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Vision for Agriculture and Food</t>
+          <t>European Climate Law amendment</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Competitiveness and Decarbonisation</t>
+          <t>Decarbonisation</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1927,28 +1927,28 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Common Agricultural Policy simplification package</t>
+          <t>Vision for Agriculture and Food</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>Competitiveness and Decarbonisation</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ocean Pact</t>
+          <t>Common Agricultural Policy simplification package</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Competitiveness</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Non-legislative</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2003,18 +2003,18 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>European Water Resilience Strategy</t>
+          <t>Ocean Pact</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preparedness and Resilience Protecting our democracy, upholding our values</t>
+          <t>Competitiveness</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2041,18 +2041,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>European Democracy Shield</t>
+          <t>European Water Resilience Strategy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Preparedness and Resilience</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EU Strategy to support, protect and empower the civil society</t>
+          <t>European Democracy Shield</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2117,18 +2117,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Roadmap for Women’s Rights</t>
+          <t>EU Strategy to support, protect and empower the civil society</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Equality</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Q1 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2155,18 +2155,18 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>New equality strategies for LGBTIQ</t>
+          <t>Roadmap for Women’s Rights</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Equality A global Europe: Leveraging our power and partnerships</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1 2025</t>
         </is>
       </c>
     </row>
@@ -2193,18 +2193,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pact for the Mediterranean</t>
+          <t>New equality strategies for LGBTIQ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -2231,18 +2231,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EU strategic approach to the Black Sea/ Black Sea Strategy</t>
+          <t>Anti-racism</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Equality</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -2269,18 +2269,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Joint Communication on a new Strategic EU-India Agenda</t>
+          <t>Pact for the Mediterranean</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Geopolitics Delivering together and preparing our Union for the future</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2307,28 +2307,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Post-2027 Multiannual Financial Framework proposals</t>
+          <t>EU strategic approach to the Black Sea/ Black Sea Strategy</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Future priority</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Non-legislative</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2340,25 +2340,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fitness check on the legislative acquis in the digital policy area</t>
+          <t>Joint Communication on a new Strategic EU-India Agenda</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2370,25 +2378,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fitness check on energy security architecture</t>
+          <t>Post-2027 Multiannual Financial Framework proposals</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Future priority</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Legislative</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2400,25 +2416,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fitness check on market access in inland waterway transport</t>
+          <t>An EU fit for enlargement: policy reviews and reforms</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Future priority</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Non-legislative</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Q2 / Q3 2025</t>
+          <t>tbd</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2459,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fitness Check of EU airports legislation</t>
+          <t>Fitness check on the legislative acquis in the digital policy area</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2465,12 +2489,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Evaluation of the Public Procurement Directives</t>
+          <t>Fitness check on energy security architecture</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2478,7 +2502,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2519,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
+          <t>Fitness check on market access in inland waterway transport</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2508,7 +2532,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 / Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2549,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7.</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
+          <t>Fitness Check of EU airports legislation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2555,12 +2579,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Evaluation of radioactive waste directives</t>
+          <t>Evaluation of the Public Procurement Directives</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2568,7 +2592,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2609,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9.</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
+          <t>Evaluation of EU rules on medical devices and in vitro diagnostics</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2615,12 +2639,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Evaluation of the EU Lifts Directive</t>
+          <t>Evaluation of the National Emission Reduction Commitments Directive</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2628,7 +2652,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2669,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
+          <t>Evaluation of radioactive waste directives</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2658,7 +2682,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2699,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
+          <t>Evaluation of the Pressure Equipment Directive and the Simple Pressure Vessels Directive</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2705,12 +2729,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Evaluation of the Fishing Vessel Safety Directive</t>
+          <t>Evaluation of the EU Lifts Directive</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2718,7 +2742,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Q1/Q2 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2759,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
+          <t>Evaluation of the Directive on Unfair trading practices in the agricultural and food supply chain</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2748,7 +2772,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2765,12 +2789,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15.</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Evaluation of State aid rules for banks in difficulties</t>
+          <t>Evaluation on the Land use, land-use change and forestry (LULUCF) Regulation</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2795,12 +2819,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>16.</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Evaluation of the Guarantee Notice</t>
+          <t>Evaluation of the Fishing Vessel Safety Directive</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2832,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q1/Q2 2025</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2849,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>17.</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
+          <t>Evaluation of the Geo-blocking Regulation (GBR)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2855,12 +2879,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>18.</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Evaluation of EU Rules of Origin</t>
+          <t>Evaluation of State aid rules for banks in difficulties</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2885,12 +2909,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>19.</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Evaluation of the Defence Transfers Directive</t>
+          <t>Evaluation of the Guarantee Notice</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2898,7 +2922,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2939,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>20.</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Evaluation of the Firearms Directive</t>
+          <t>Evaluation of the Anti-tax Avoidance Directive (ATAD)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2945,12 +2969,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>21.</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Evaluation on the Innovation Fund</t>
+          <t>Evaluation of EU Rules of Origin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2975,12 +2999,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>22.</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Evaluation on the Modernisation Fund</t>
+          <t>Evaluation of the Defence Transfers Directive</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3005,12 +3029,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>23.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
+          <t>Evaluation of the Firearms Directive</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3018,7 +3042,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3059,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
+          <t>Evaluation on the Innovation Fund</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3048,7 +3072,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Q3/Q4 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3089,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>25.</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
+          <t>Evaluation on the Modernisation Fund</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3078,7 +3102,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3119,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>26.</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
+          <t>Evaluation of Regulation (EU) 2016/796 of EU Agency for Railways</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3108,7 +3132,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3149,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>27.</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
+          <t>Ex-post evaluation of Connecting Europe Facility (CEF) 2014-2020</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3138,7 +3162,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3/Q4 2025</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3179,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>28.</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
+          <t>Ex-post evaluation of Asylum, Migration, and Integration Fund (AMIF) 2014-2020</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3185,12 +3209,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>29.</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
+          <t>Ex-post evaluation of the Internal Security Fund – Borders and Visa (ISF-BV) 2014-2020</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3215,12 +3239,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>30.</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
+          <t>Ex-post evaluation of the Internal Security Fund – Police (ISF-P) 2014-2020</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3228,7 +3252,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3269,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the European Defence Fund</t>
+          <t>Ex-post evaluation of the European Regional Development Fund and the Cohesion Fund 2014-2020</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3258,7 +3282,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Q1-Q2 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3299,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>32.</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs 2021-2027 programme</t>
+          <t>Ex post evaluation of the Fund for European Aid to the Most Deprived (FEAD) 2014-2020</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3288,7 +3312,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3329,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>33.</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
+          <t>Ex post evaluation of European Social Fund and Youth Employment Initiative 2014-2020</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3318,7 +3342,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3359,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>34.</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
+          <t>Interim Evaluation of the European Defence Fund</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3348,7 +3372,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q1-Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3360,17 +3384,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>35.</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
+          <t>Interim evaluation of the Customs 2021-2027 programme</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3378,7 +3402,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3414,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>36.</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
+          <t>Interim evaluation of the Customs Control Equipment Instrument (CCEI) programme</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3420,17 +3444,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>37.</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
+          <t>Interim Evaluation of the Fiscalis 2021-2027 programme</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3438,7 +3462,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q4 2025</t>
         </is>
       </c>
     </row>
@@ -3450,33 +3474,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>COM(2011)714 final Proposal for a COUNCIL DIRECTIVE on a common system of taxation Obsolete – the scope of the proposal has been partly</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2011/0314 (CNS) applicable to interest and royalty payments made between associated companies taken over by the Directive implementing the OECD of different Member States Pillar 2 on minimum corporate taxation. The remaining issues the proposal intended to tackle will be addressed via an upcoming Omnibus act as a part of the simplification process.</t>
-        </is>
-      </c>
+          <t>Interim evaluation of the Horizon Europe framework programme for Research and Innovation</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3488,33 +3504,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>COM(2011)827 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the proposal is by now obsolete. The</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2011/0391 (COD) THE COUNCIL on common rules for the allocation of slots at European Union Commission has launched a fitness-check and will airports decide on the basis of its findings on the way forward.</t>
-        </is>
-      </c>
+          <t>Mid-term evaluation of the European Regional Development Fund, the Cohesion Fund and the Just Transition Fund 2021-2027</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3526,33 +3534,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>COM(2012)336 final Proposal for a COUNCIL REGULATION establishing a facility for providing Obsolete – the proposal needs to be updated as regards</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2012/0164 (APP) financial assistance for Member States whose currency is not the euro i.a. the funding modalities of the Balance of Payments Facility and to integrate the lessons to be drawn from the recent crises, as well as the institutional, economic and financial sector developments since 2009, and their possible implication for the design and implementation of the facility, in line with the Council Conclusions of 27 March 2024.</t>
-        </is>
-      </c>
+          <t>Mid-term evaluation of the European Social Fund Plus 2021-2027</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>Q2 2025</t>
         </is>
       </c>
     </row>
@@ -3569,30 +3569,26 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>COM(2015)603 final Proposal for a COUNCIL DECISION laying down measures in view of No foreseeable agreement – in the context of the</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on a common system of taxation applicable to interest and royalty payments made between associated companies of different Member States</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2015/0250 (NLE) progressively establishing unified representation of the euro area in the discussions on Europe’s economic and financial International Monetary Fund sovereignty, the Commission will assess whether another proposal should be tabled or another type of approach should be chosen. 2 This list includes pending legislative proposals, which the Commission intends to withdraw within six months 22 No. References Title Reasons for withdrawal</t>
+          <t>References: COM(2011)714 final 2011/0314 (CNS) Reasons for withdrawal: Obsolete – the scope of the proposal has been partly taken over by the Directive implementing the OECD Pillar 2 on minimum corporate taxation. The remaining issues the proposal intended to tackle will be addressed via an upcoming Omnibus act as a part of the simplification process.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3607,30 +3603,26 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>COM(2017)276 final Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the No foreseeable agreement – the proposal is blocked with</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on common rules for the allocation of slots at European Union airports</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2017/0115 (CNS) charging of heavy goods vehicles for the use of certain infrastructures, as regards no perspective of agreement. certain provisions on vehicle taxation</t>
+          <t>References: COM(2011)827 final 2011/0391 (COD) Reasons for withdrawal: Obsolete – the proposal is by now obsolete. The Commission has launched a fitness-check and will decide on the basis of its findings on the way forward.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3645,17 +3637,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>COM(2017)647 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal has not been</t>
+          <t>Proposal for a COUNCIL REGULATION establishing a facility for providing financial assistance for Member States whose currency is not the euro</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2017/0288 (COD) THE COUNCIL amending Regulation (EC) No 1073/2009 on common rules for taken up for discussion in the Council and is by now access to the international market for coach and bus services outdated.</t>
+          <t>References: COM(2012)336 final 2012/0164 (APP) Reasons for withdrawal: Obsolete – the proposal needs to be updated as regards i.a. the funding modalities of the Balance of Payments Facility and to integrate the lessons to be drawn from the recent crises, as well as the institutional, economic and financial sector developments since 2009, and their possible implication for the design and implementation of the facility, in line with the Council Conclusions of 27 March 2024.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3664,11 +3656,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3683,30 +3671,26 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>COM(2017)827 final Proposal for a COUNCIL REGULATION on the establishment of the European No foreseeable agreement - many of the changes</t>
+          <t>Proposal for a COUNCIL DECISION laying down measures in view of progressively establishing unified representation of the euro area in the International Monetary Fund</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2017/0333 (APP) Monetary Fund proposed under this initiative have been incorporated into a separate revision of the European Stability Mechanism Treaty.</t>
+          <t>References: COM(2015)603 final 2015/0250 (NLE) Reasons for withdrawal: No foreseeable agreement – in the context of the discussions on Europe’s economic and financial sovereignty, the Commission will assess whether another proposal should be tabled or another type of approach should be chosen.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3721,17 +3705,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>COM(2018)135 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a COUNCIL DIRECTIVE amending Directive 1999/62/EC on the charging of heavy goods vehicles for the use of certain infrastructures, as regards certain provisions on vehicle taxation</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2018/0063B (COD) THE COUNCIL on credit servicers, credit purchasers and the recovery of further progress is unlikely. collateral</t>
+          <t>References: COM(2017)276 final 2017/0115 (CNS) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked with no perspective of agreement.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -3740,11 +3724,7 @@
           <t>DIRECTIVE</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3759,30 +3739,26 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>COM(2018)329 final Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as No foreseeable agreement – discussions are suspended</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1073/2009 on common rules for access to the international market for coach and bus services</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2018/0164(CNS) regards the introduction of the detailed technical measures for the operation of since 2019 and further progress is unlikely. the definitive VAT system for the taxation of trade between Member States</t>
+          <t>References: COM(2017)647 final 2017/0288 (COD) Reasons for withdrawal: No foreseeable agreement – the proposal has not been taken up for discussion in the Council and is by now outdated.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3797,17 +3773,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>COM(2018)339 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a COUNCIL REGULATION on the establishment of the European Monetary Fund</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2018/0171 (COD) THE COUNCIL on sovereign bond-backed securities further progress is unlikely.</t>
+          <t>References: COM(2017)827 final 2017/0333 (APP) Reasons for withdrawal: No foreseeable agreement - many of the changes proposed under this initiative have been incorporated into a separate revision of the European Stability Mechanism Treaty.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3816,11 +3792,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3835,30 +3807,26 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>COM(2018)387 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - The proposal is outdated</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on credit servicers, credit purchasers and the recovery of collateral</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2018/0212 (COD) THE COUNCIL on the establishment of a European Investment Stabilisation with the entry into force of NGEU and the Recovery and Function Resilience Facility (RRF) and the withdrawal of the so- called Budgetary Instrument for Convergence and Competitiveness (BICC) in February 2021.</t>
+          <t>References: COM(2018)135 final 2018/0063B (COD) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3873,30 +3841,26 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>COM(2019)38 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
+          <t>Proposal for a COUNCIL DIRECTIVE amending Directive 2006/112/EC as regards the introduction of the detailed technical measures for the operation of the definitive VAT system for the taxation of trade between Member States</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2019/0017 (COD) THE COUNCIL amending Regulation (EU) 2015/757 in order to take incorporated into the most recent EU ETS revision, appropriate account of the global data collection system for ship fuel oil adopted in 2023. consumption data</t>
+          <t>References: COM(2018)329 final 2018/0164(CNS) Reasons for withdrawal: No foreseeable agreement – discussions are suspended since 2019 and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3911,30 +3875,26 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>COM(2020)49 final Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field Obsolete - since the adoption of this proposal in 2020, a</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on sovereign bond-backed securities</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2020/0022 (CNS) of taxation (codification) number of significant amendments have been adopted, making this codification proposal obsolete. The Commission will propose a new codified proposal. 23 No. References Title Reasons for withdrawal</t>
+          <t>References: COM(2018)339 final 2018/0171 (COD) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3949,17 +3909,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>COM(2020)577 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – changes contained in this proposal have been</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the establishment of a European Investment Stabilisation Function</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2020/0264 (COD) THE COUNCIL amending Regulation (EU) 2018/1139 as regards the capacity incorporated into the Single European Sky ("SES II +") of the European Union Aviation Safety Agency to act as Performance Review Regulation. Body of the Single European Sky</t>
+          <t>References: COM(2018)387 final 2018/0212 (COD) Reasons for withdrawal: No foreseeable agreement - The proposal is outdated with the entry into force of NGEU and the Recovery and Resilience Facility (RRF) and the withdrawal of the so- called Budgetary Instrument for Convergence and Competitiveness (BICC) in February 2021.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -3968,11 +3928,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3987,30 +3943,26 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>COM(2021)769 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - since the adoption of this proposal in 2021, a</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2015/757 in order to take appropriate account of the global data collection system for ship fuel oil consumption data</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2021/0400 (COD) THE COUNCIL laying down for certain road vehicles circulating within the recent amendment has been proposed by the Union the maximum authorised dimensions in national and international traffic Commission, that will make this codification proposal and the maximum authorised weights in international traffic (codification) obsolete. The Commission will propose a new codified proposal as soon as the new amendment will have been adopted.</t>
+          <t>References: COM(2019)38 final 2019/0017 (COD) Reasons for withdrawal: Obsolete – changes contained in this proposal have been incorporated into the most recent EU ETS revision, adopted in 2023.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4025,17 +3977,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>COM(2022)222 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the changes suggested by this proposal were</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on administrative cooperation in the field of taxation (codification)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2022/0160 (COD) THE COUNCIL amending Directive (EU) 2018/2001 on the promotion of the incorporated during the discussions on the revision of use of energy from renewable sources, Directive 2010/31/EU on the energy the Energy Performance of Buildings Directive, the performance of buildings and Directive 2012/27/EU on energy efficiency Energy Efficiency Directive and the Renewable Energy Directive.</t>
+          <t>References: COM(2020)49 final 2020/0022 (CNS) Reasons for withdrawal: Obsolete - since the adoption of this proposal in 2020, a number of significant amendments have been adopted, making this codification proposal obsolete. The Commission will propose a new codified proposal.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4044,11 +3996,7 @@
           <t>DIRECTIVE</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4063,17 +4011,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>COM(2023)232 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2018/1139 as regards the capacity of the European Union Aviation Safety Agency to act as Performance Review Body of the Single European Sky</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2023/0133(COD) THE COUNCIL on standard essential patents and amending Regulation whether another proposal should be tabled or another (EU)2017/1001 type of approach should be chosen. A new era for European Defence and Security</t>
+          <t>References: COM(2020)577 final 2020/0264 (COD) Reasons for withdrawal: Obsolete – changes contained in this proposal have been incorporated into the Single European Sky ("SES II +") Regulation.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4082,11 +4030,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4101,17 +4045,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>COM(2018)634 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the Commission intends to present a new</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL laying down for certain road vehicles circulating within the Union the maximum authorised dimensions in national and international traffic and the maximum authorised weights in international traffic (codification)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2018/0329 (COD) THE COUNCIL on common standards and procedures in Member States for proposal in 2025 (referred to in annex 1 of this returning illegally staying third-country nationals (recast) A contribution from Commission Work Programme) in the context of which the European Commission to the Leaders’ meeting in Salzburg on 19-20 the current pending proposal will be effectively September 2018 withdrawn.</t>
+          <t>References: COM(2021)769 final 2021/0400 (COD) Reasons for withdrawal: Obsolete - since the adoption of this proposal in 2021, a recent amendment has been proposed by the Commission, that will make this codification proposal obsolete. The Commission will propose a new codified proposal as soon as the new amendment will have been adopted.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4120,11 +4064,7 @@
           <t>DIRECTIVE</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4139,30 +4079,26 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>COM(2021)890 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete – the content of this proposal was merged into</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Directive (EU) 2018/2001 on the promotion of the use of energy from renewable sources, Directive 2010/31/EU on the energy performance of buildings and Directive 2012/27/EU on energy efficiency</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2021/0427 (COD) THE COUNCIL addressing situations of instrumentalisation in the field of Regulation (EU) 2024/1359 addressing situations of migration and asylum crisis and force majeure in the field of migration and asylum and amending Regulation (EU) 2021/1147.</t>
+          <t>References: COM(2022)222 final 2022/0160 (COD) Reasons for withdrawal: Obsolete – the changes suggested by this proposal were incorporated during the discussions on the revision of the Energy Performance of Buildings Directive, the Energy Efficiency Directive and the Renewable Energy Directive.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4177,30 +4113,26 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>COM(2021)752 final Proposal for a COUNCIL DECISION on provisional emergency measures for Obsolete – the proposal was blocked during the inter-</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on standard essential patents and amending Regulation (EU)2017/1001</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2021/0401 (CNS) the benefit of Latvia, Lithuania and Poland institutional discussions and is now obsolete. 24 No. References Title Reasons for withdrawal</t>
+          <t>References: COM(2023)232 final 2023/0133(COD) Reasons for withdrawal: No foreseeable agreement - the Commission will assess whether another proposal should be tabled or another type of approach should be chosen.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4215,30 +4147,26 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>COM(2024)174 final Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Obsolete – no agreement was foreseeable. The Schengen</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on common standards and procedures in Member States for returning illegally staying third-country nationals (recast) A contribution from the European Commission to the Leaders’ meeting in Salzburg on 19-20 September 2018</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024/0094 (NLE) Cycle Council agreed on a number of priority areas for action that are dealt with via other means than this proposal. Sustaining our quality of life: food security, water and nature</t>
+          <t>References: COM(2018)634 final 2018/0329 (COD) Reasons for withdrawal: Obsolete - the Commission intends to present a new proposal in 2025 (referred to in annex 1 of this Commission Work Programme) in the context of which the current pending proposal will be effectively withdrawn.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4253,17 +4181,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>COM(2012)403 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL addressing situations of instrumentalisation in the field of migration and asylum</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2012/0196 (COD) THE COUNCIL on the protection of species of wild fauna and flora by regulating Furthermore, since 2012, developments took place that trade therein (Recast) make this proposal obsolete. The Commission will assess whether another proposal should be tabled or another type of approach should be chosen to allow for a new start.</t>
+          <t>References: COM(2021)890 final 2021/0427 (COD) Reasons for withdrawal: Obsolete – the content of this proposal was merged into Regulation (EU) 2024/1359 addressing situations of crisis and force majeure in the field of migration and asylum and amending Regulation (EU) 2021/1147.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -4272,11 +4200,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4291,30 +4215,26 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>COM(2015)177 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - any potential further</t>
+          <t>Proposal for a COUNCIL DECISION on provisional emergency measures for the benefit of Latvia, Lithuania and Poland</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2015/0093 (COD) THE COUNCIL amending Regulation (EC) No 1829/2003 as regards the amendment of the GMO legislation will depend on the possibility for the Member States to restrict or prohibit the use of genetically outcome of the negotiations on the proposal for new modified food and feed on their territory genomic techniques, or the identification of issues to be addressed in the context of the biotechnology and biomanufacturing initiative.</t>
+          <t>References: COM(2021)752 final 2021/0401 (CNS) Reasons for withdrawal: Obsolete – the proposal was blocked during the inter- institutional discussions and is now obsolete.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4329,30 +4249,26 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>COM(2022)563 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a COUNCIL RECOMMENDATION for the 2024/2025 Schengen Cycle</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2022/0348 (COD) THE COUNCIL laying down management, conservation and control measures between the European Parliament and the Council at applicable in the Area of the Southern Indian Ocean Fisheries Agreement first reading. The Commission intends to present a new (SIOFA) proposal in 2025 in the context of which the current pending proposal will be effectively withdrawn.</t>
+          <t>References: COM(2024)174 final 2024/0094 (NLE) Reasons for withdrawal: Obsolete – no agreement was foreseeable. The Schengen Council agreed on a number of priority areas for action that are dealt with via other means than this proposal.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4367,17 +4283,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>COM(2023)771 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the protection of species of wild fauna and flora by regulating trade therein (Recast)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2023/0449 (COD) THE COUNCIL amending Regulations (EU) 2016/1139, (EU) 2018/973 and from the colegislators. (EU) 2019/472 as regards the targets for fixing fishing opportunities Protecting our democracy, upholding our values</t>
+          <t>References: COM(2012)403 final 2012/0196 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected. Furthermore, since 2012, developments took place that make this proposal obsolete. The Commission will assess whether another proposal should be tabled or another type of approach should be chosen to allow for a new start.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -4386,11 +4302,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4405,30 +4317,26 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>COM(2008)426 final Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1829/2003 as regards the possibility for the Member States to restrict or prohibit the use of genetically modified food and feed on their territory</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2008/0140 (CNS) treatment between persons irrespective of religion or belief, disability, age or further progress is unlikely. sexual orientation 25 No. References Title Reasons for withdrawal</t>
+          <t>References: COM(2015)177 final 2015/0093 (COD) Reasons for withdrawal: No foreseeable agreement - any potential further amendment of the GMO legislation will depend on the outcome of the negotiations on the proposal for new genomic techniques, or the identification of issues to be addressed in the context of the biotechnology and biomanufacturing initiative.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4443,17 +4351,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>COM(2011)137 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement - no progress has been made</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL laying down management, conservation and control measures applicable in the Area of the Southern Indian Ocean Fisheries Agreement (SIOFA)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2011/0073 (COD) OF THE COUNCIL amending Regulation (EC) No 1049/2001 regarding public since 2011. access to European Parliament, Council and Commission documents COM(2008)229 final 2008/0090 (COD)</t>
+          <t>References: COM(2022)563 final 2022/0348 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected between the European Parliament and the Council at first reading. The Commission intends to present a new proposal in 2025 in the context of which the current pending proposal will be effectively withdrawn.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4462,11 +4370,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4481,17 +4385,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>COM(2016)799 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulations (EU) 2016/1139, (EU) 2018/973 and (EU) 2019/472 as regards the targets for fixing fishing opportunities</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2016/0400B (COD) OF THE COUNCIL adapting a number of legal acts providing for the use of the further progress is unlikely. There is a legal obligation regulatory procedure with scrutiny to Articles 290 and 291 of the Treaty on the to put legal acts adopted prior to the entry into force of Functioning of the European Union the Treaty of Lisbon in conformity with Articles 290 and 291 TFEU. The Commission will therefore present to the colegislators a new proposal to that effect.</t>
+          <t>References: COM(2023)771 final 2023/0449 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected from the colegislators.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -4500,11 +4404,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4519,30 +4419,26 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>COM(2017)10 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected</t>
+          <t>Proposal for a COUNCIL DIRECTIVE on implementing the principle of equal treatment between persons irrespective of religion or belief, disability, age or sexual orientation</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2017/0003 (COD) THE COUNCIL concerning the respect for private life and the protection of from the colegislators. Furthermore, the proposal is personal data in electronic communications and repealing Directive 2002/58/EC outdated in view of some recent legislation in both the (Regulation on Privacy and Electronic Communications technological and the legislative landscape.</t>
+          <t>References: COM(2008)426 final 2008/0140 (CNS) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4557,17 +4453,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>COM(2017)85 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EC) No 1049/2001 regarding public access to European Parliament, Council and Commission documents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2017/0035 (COD) THE COUNCIL amending Regulation (EU) No 182/2011 laying down the rules further progress is unlikely. and general principles concerning mechanisms for control by Member States of the Commission’s exercise of implementing powers</t>
+          <t>References: COM(2011)137 final 2011/0073 (COD) COM(2008)229 final 2008/0090 (COD) Reasons for withdrawal: No foreseeable agreement - no progress has been made since 2011.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -4576,11 +4472,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4595,17 +4487,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>COM(2018)96 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – the proposal is blocked and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL adapting a number of legal acts providing for the use of the regulatory procedure with scrutiny to Articles 290 and 291 of the Treaty on the Functioning of the European Union</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2018/0044 (COD) THE COUNCIL on the law applicable to the third-party effects of assignments further progress is unlikely. of claims</t>
+          <t>References: COM(2016)799 final 2016/0400B (COD) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely. There is a legal obligation to put legal acts adopted prior to the entry into force of the Treaty of Lisbon in conformity with Articles 290 and 291 TFEU. The Commission will therefore present to the colegislators a new proposal to that effect.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -4614,11 +4506,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4633,30 +4521,26 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>COM(2022)496 final Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement - the Commission will assess</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL concerning the respect for private life and the protection of personal data in electronic communications and repealing Directive 2002/58/EC (Regulation on Privacy and Electronic Communications</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2022/0303 (COD) THE COUNCIL on adapting non-contractual civil liability rules to artificial whether another proposal should be tabled or another intelligence (AI Liability) type of approach should be chosen. A global Europe: Leveraging our power and partnerships</t>
+          <t>References: COM(2017)10 final 2017/0003 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected from the colegislators. Furthermore, the proposal is outdated in view of some recent legislation in both the technological and the legislative landscape.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIRECTIVE</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4671,30 +4555,26 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JOIN(2015)36 final Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the Obsolete – the ratification process of this agreement has</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) No 182/2011 laying down the rules and general principles concerning mechanisms for control by Member States of the Commission’s exercise of implementing powers</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2015/0302 (NLE) European Union, of the Cooperation Agreement on Partnership and Development been interrupted with the establishment of a Taliban between the European Union and the Islamic Republic of Afghanistan appointed caretaker government that, to date, remains unrecognized by the international community, making the original agreement obsolete. 26 No. References Title Reasons for withdrawal</t>
+          <t>References: COM(2017)85 final 2017/0035 (COD) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4709,30 +4589,26 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COM(2022)63 final Proposal for a COUNCIL DECISION on the position to be taken on behalf of the Obsolete - the proposal was made in the negotiations on</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on the law applicable to the third-party effects of assignments of claims</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2022/0043 (NLE) European Union in the written procedure by the Participants to the Arrangement the modernisation of the Arrangement on Officially on Officially Supported Export Credits amending Annex IV Supported Export Credits, which were finalised in 2023. The content of this proposal was included in another Council decision making this one redundant. Delivering together and preparing our Union for the future</t>
+          <t>References: COM(2018)96 final 2018/0044 (COD) Reasons for withdrawal: No foreseeable agreement – the proposal is blocked and further progress is unlikely.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4747,30 +4623,26 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>COM(2022)184 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF Obsolete - the content of the proposal has been adopted</t>
+          <t>Proposal for a DIRECTIVE OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL on adapting non-contractual civil liability rules to artificial intelligence (AI Liability)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2022/0125 (COD) THE COUNCIL amending Regulation (EU, Euratom) 2018/1046 on the financial end of September 2024 as part of the revision of the rules applicable to the general budget of the Union Financial Regulation (Recast).</t>
+          <t>References: COM(2022)496 final 2022/0303 (COD) Reasons for withdrawal: No foreseeable agreement - the Commission will assess whether another proposal should be tabled or another type of approach should be chosen.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>DIRECTIVE</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4785,30 +4657,26 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>COM(2024)301 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Joint Proposal for a COUNCIL DECISION on the conclusion, on behalf of the European Union, of the Cooperation Agreement on Partnership and Development between the European Union and the Islamic Republic of Afghanistan</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024/0059 (COD) THE COUNCIL amending Regulation (EU) 2021/1148 as regards the financial Furthermore, the MFF mid-term revision can be envelope and the allocation for the thematic facility implemented without this legal proposal.</t>
+          <t>References: JOIN(2015)36 final 2015/0302 (NLE) Reasons for withdrawal: Obsolete – the ratification process of this agreement has been interrupted with the establishment of a Taliban appointed caretaker government that, to date, remains unrecognized by the international community, making the original agreement obsolete.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4823,30 +4691,26 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>COM(2024)100 final Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF No foreseeable agreement – no agreement is expected.</t>
+          <t>Proposal for a COUNCIL DECISION on the position to be taken on behalf of the European Union in the written procedure by the Participants to the Arrangement on Officially Supported Export Credits amending Annex IV</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024/0060 (COD) THE COUNCIL amending Regulation (EU) No 2021/522, Regulation (EU) No The MFF mid-term revision can be implemented 2021/1057, Regulation (EU) No 2021/1060, Regulation (EU) No 2021/1139, without this legal proposal. An amendment to the Regulation (EU) No 2021/1229 and Regulation (EU) No 2021/1775 as regards Regulation 2021/1755 establishing the Brexit the changes to the amounts of funds for certain programmes and funds Adjustment Reserve (BAR) to establish the legal basis for redistribution of the outstanding amounts between the Member States will be proposed by the Commission in 2025. 27 Annex V: Envisaged repeals No. Policy area Title Reasons for repeal</t>
+          <t>References: COM(2022)63 final 2022/0043 (NLE) Reasons for withdrawal: Obsolete - the proposal was made in the negotiations on the modernisation of the Arrangement on Officially Supported Export Credits, which were finalised in 2023. The content of this proposal was included in another Council decision making this one redundant.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>REGULATION</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4861,17 +4725,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Agriculture Council Regulation (EC)No 870/2004 of 26 This Community programme was established for the period 2004 to 2006 to complement and</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU, Euratom) 2018/1046 on the financial rules applicable to the general budget of the Union</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>April 2004 establishing a Community promote, at Community level, the work undertaken in the Member States for the conservation, programme on the conservation, characterisation, collection and utilisation of genetic resources in agriculture. Support under this characterisation, collection and utilisation of programme is no longer available, since all Common Agricultural Policy (CAP) support is currently genetic resources in agriculture and repealing granted under the ongoing rural development programmes (until 2025) and national CAP Strategic Regulation (EC) No 1467/94 Plans (until 2027), following Regulation (EU) 1305/2013 and Regulation (EU) 2021/2115 respectively, making this regulation obsolete.</t>
+          <t>References: COM(2022)184 final 2022/0125 (COD) Reasons for withdrawal: Obsolete - the content of the proposal has been adopted end of September 2024 as part of the revision of the Financial Regulation (Recast).</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4880,11 +4744,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4899,17 +4759,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>European statistics Council Regulation (EEC) No 3037/90 of 9 The classification from 1990 is obsolete. The current statistical classification of economic</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) 2021/1148 as regards the financial envelope and the allocation for the thematic facility</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>October 1990 on the statistical classification of activities’ in the European Community (NACE) is established in Regulation (EC) No 1893/2006 economic activities in the European of the European Parliament and of the Council of 20 December 2006, as last amended by Community Commission Delegated Regulation (EU) 2023/137 of 10 October 2022.</t>
+          <t>References: COM(2024)301 final 2024/0059 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected. Furthermore, the MFF mid-term revision can be implemented without this legal proposal.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4918,11 +4778,7 @@
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4937,23 +4793,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>European statistics Council Decision of 25 June 1996 on improving The Decision is obsolete. It has been superseded by new regulations on agricultural statistics</t>
+          <t>Proposal for a REGULATION OF THE EUROPEAN PARLIAMENT AND OF THE COUNCIL amending Regulation (EU) No 2021/522, Regulation (EU) No 2021/1057, Regulation (EU) No 2021/1060, Regulation (EU) No 2021/1139, Regulation (EU) No 2021/1229 and Regulation (EU) No 2021/1775 as regards the changes to the amounts of funds for certain programmes and funds</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Community agricultural statistics (96/411/EC) (integrated farm statistics, agricultural input and output, economic accounts for agriculture).</t>
+          <t>References: COM(2024)100 final 2024/0060 (COD) Reasons for withdrawal: No foreseeable agreement – no agreement is expected. The MFF mid-term revision can be implemented without this legal proposal. An amendment to the Regulation 2021/1755 establishing the Brexit Adjustment Reserve (BAR) to establish the legal basis for redistribution of the outstanding amounts between the Member States will be proposed by the Commission in 2025.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>REGULATION</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -4966,35 +4822,149 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Council Regulation (EC)No 870/2004 of 26 April 2004 establishing a Community programme on the conservation, characterisation, collection and utilisation of genetic resources in agriculture and repealing Regulation (EC) No 1467/94</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Reasons for repeal: This Community programme was established for the period 2004 to 2006 to complement and promote, at Community level, the work undertaken in the Member States for the conservation, characterisation, collection and utilisation of genetic resources in agriculture. Support under this programme is no longer available, since all Common Agricultural Policy (CAP) support is currently granted under the ongoing rural development programmes (until 2025) and national CAP Strategic Plans (until 2027), following Regulation (EU) 1305/2013 and Regulation (EU) 2021/2115 respectively, making this regulation obsolete.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>WP128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Council Regulation (EEC) No 3037/90 of 9 October 1990 on the statistical classification of economic activities in the European Community</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Reasons for repeal: The classification from 1990 is obsolete. The current statistical classification of economic activities’ in the European Community (NACE) is established in Regulation (EC) No 1893/2006 of the European Parliament and of the Council of 20 December 2006, as last amended by Commission Delegated Regulation (EU) 2023/137 of 10 October 2022.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>European statistics</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>REGULATION</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>WP129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Council Decision of 25 June 1996 on improving Community agricultural statistics (96/411/EC)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Reasons for repeal: The Decision is obsolete. It has been superseded by new regulations on agricultural statistics (integrated farm statistics, agricultural input and output, economic accounts for agriculture).</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>European statistics</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WP130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Road freight Council Regulation (EEC) No 4058/89 of 21 Modern EU legislation has introduced a comprehensive framework that regulates road transport,</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>transport December 1989 on the fixing of rates for the focusing on safety, environmental standards, and fair competition without the need for rate-fixing. carriage of goods by road between Member Regulations such as Regulation (EC) No 1071/2009, Regulation (EC) No 1072/2009, and States Regulation (EC) No 1073/2009 have effectively superseded the need for the provisions outlined in Council Regulation (EEC) No 4058/89, rendering it redundant. 28</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Council Regulation (EEC) No 4058/89 of 21 December 1989 on the fixing of rates for the carriage of goods by road between Member States</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Reasons for repeal: Modern EU legislation has introduced a comprehensive framework that regulates road transport, focusing on safety, environmental standards, and fair competition without the need for rate-fixing. Regulations such as Regulation (EC) No 1071/2009, Regulation (EC) No 1072/2009, and Regulation (EC) No 1073/2009 have effectively superseded the need for the provisions outlined in Council Regulation (EEC) No 4058/89, rendering it redundant.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Road freight transport</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>REGULATION</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
